--- a/output/pdf_financials_xlsx/KTRI.xlsx
+++ b/output/pdf_financials_xlsx/KTRI.xlsx
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.041251</v>
+        <v>-0.041251</v>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         <v>-0.227506</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.160018</v>
+        <v>-0.160018</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.103506</v>
+        <v>-0.103506</v>
       </c>
     </row>
     <row r="17">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.041251</v>
+        <v>-0.041251</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
@@ -965,10 +965,10 @@
         <v>-0.227506</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.160018</v>
+        <v>-0.160018</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.103506</v>
+        <v>-0.103506</v>
       </c>
     </row>
     <row r="21">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.041251</v>
+        <v>-0.041251</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.041251</v>
@@ -1044,10 +1044,10 @@
         <v>-0.227506</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.160018</v>
+        <v>-0.160018</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.103506</v>
+        <v>-0.103506</v>
       </c>
     </row>
     <row r="24">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.041251</v>
+        <v>-0.041251</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         <v>-0.227506</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.160018</v>
+        <v>-0.160018</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.103506</v>
+        <v>-0.103506</v>
       </c>
     </row>
     <row r="28">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.042628</v>
+        <v>-0.039874</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
         <v>-0.223457</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.162852</v>
+        <v>-0.157184</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.10549</v>
+        <v>-0.101522</v>
       </c>
     </row>
     <row r="30">
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2935,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.075985</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.319682</v>
       </c>
     </row>
     <row r="93">
@@ -4804,7 +4804,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -8320,10 +8324,10 @@
         </is>
       </c>
       <c r="I96" s="5" t="n">
-        <v>0.160018</v>
+        <v>-0.160018</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>0.103506</v>
+        <v>-0.103506</v>
       </c>
     </row>
     <row r="97">
@@ -8853,10 +8857,10 @@
         </is>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0.227506</v>
+        <v>-0.227506</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>0.160018</v>
+        <v>-0.160018</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -9494,10 +9498,10 @@
         </is>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.254406</v>
+        <v>-0.254406</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>0.227506</v>
+        <v>-0.227506</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -10560,7 +10564,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0.041251</v>
+        <v>-0.041251</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/KTRI.xlsx
+++ b/output/pdf_financials_xlsx/KTRI.xlsx
@@ -1352,7 +1352,7 @@
         <v>0.019481</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.125256</v>
       </c>
     </row>
     <row r="35">
@@ -1406,7 +1406,7 @@
         <v>0.019481</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.02</v>
+        <v>0.145256</v>
       </c>
     </row>
     <row r="37">
@@ -1730,7 +1730,7 @@
         <v>0.104249</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.224801</v>
+        <v>0.09954499999999999</v>
       </c>
     </row>
     <row r="49">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4376,7 +4376,11 @@
           <t>Exploration advances and reclamation deposits</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KTRI.xlsx
+++ b/output/pdf_financials_xlsx/KTRI.xlsx
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-0.254406</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.227506</v>
+        <v>-0.295968</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.160018</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.103506</v>
+        <v>-0.152329</v>
       </c>
     </row>
     <row r="17">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.254406</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>0.068462</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.160018</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>0.048823</v>
       </c>
     </row>
     <row r="18">
@@ -1154,16 +1154,16 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.254406</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.227506</v>
+        <v>-0.295968</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.160018</v>
+        <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.103506</v>
+        <v>-0.152329</v>
       </c>
     </row>
     <row r="28">
@@ -1208,16 +1208,16 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.248622</v>
+        <v>0.005784</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.223457</v>
+        <v>-0.291919</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.157184</v>
+        <v>0.002834</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.101522</v>
+        <v>-0.150345</v>
       </c>
     </row>
     <row r="30">
@@ -1271,17 +1271,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>-0</v>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-23.13155476267704</v>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-32.05102114502163</v>
       </c>
     </row>
     <row r="32">
@@ -6646,7 +6650,11 @@
           <t>Receipt from private placement</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -7484,7 +7492,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E77" s="5" t="n">
         <v>0.3525</v>
       </c>
@@ -8216,7 +8228,11 @@
           <t>Loss before income tax recovery $</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -8258,7 +8274,11 @@
           <t>Income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -9396,7 +9416,11 @@
           <t>Loss &amp; comprehensive loss for the year before income tax recovery $</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -9440,7 +9464,11 @@
           <t>Income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
